--- a/docs/PRAP_Programming_Specification_v0.3.xlsx
+++ b/docs/PRAP_Programming_Specification_v0.3.xlsx
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>The set of periods a project carries depends on its type: 'Clinical Trial' uses Before-Start-up / Start-up / Conduct / Close-out (interim) / Close-out</t>
+          <t>The set of periods a project carries depends on its type: either clinical trial type uses Before-Start-up / Start-up / Conduct / Close-out (interim) /</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>A 'Clinical Trial' project records its clinical phase (phase 1 / 2 / 3 / 4). The phase determines the project's period weights, so it drives the simul</t>
+          <t xml:space="preserve">A clinical trial of either type records its clinical phase (phase 1 / 2 / 3 / 4). The phase determines the project's period weights, so it drives the </t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>A 'Clinical Trial' project records who performs each of EDC set-up, data-review-system set-up, RBQM set-up and DM conduct ('by CRO' / 'by SB').</t>
+          <t>A clinical trial of either type records who performs each of EDC set-up, data-review-system set-up, RBQM set-up and DM conduct ('by CRO' / 'by SB').</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>A 'Clinical Trial' project records the EDC system, data review system and RBQM system in use, from data-driven value lists.</t>
+          <t>A clinical trial of either type records the EDC system, data review system and RBQM system in use, from data-driven value lists.</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>For a 'Clinical Trial' project, period boundaries are computed from milestone dates plus fixed month offsets (sheet 05), so a timeline change re-shape</t>
+          <t>For a clinical trial of either type, period boundaries are computed from milestone dates plus fixed month offsets (sheet 05), so a timeline change re-</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>project_category empty where project_type = 'Clinical Trial'.</t>
+          <t>project_category empty on either clinical trial type.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -4739,7 +4739,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Period derivation - 'Clinical Trial'   [REQ-CAL-09, REQ-CAL-12, REQ-CAL-13]</t>
+          <t>Period derivation - clinical trial, either type   [REQ-CAL-09, REQ-CAL-12, REQ-CAL-13]</t>
         </is>
       </c>
     </row>
